--- a/astro-site/public/dl/guia-restaurante-casual/plantilla-turnos-brigada.xlsx
+++ b/astro-site/public/dl/guia-restaurante-casual/plantilla-turnos-brigada.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnos Semana" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Turnos Semana'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -499,9 +501,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -521,6 +523,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -549,10 +552,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-casual · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -561,7 +573,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -570,7 +591,7 @@
   <sheetPr>
     <tabColor rgb="00607D8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -601,6 +622,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1251,6 +1273,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="11" t="inlineStr">
@@ -1259,6 +1282,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
@@ -1277,6 +1301,15 @@
       <formula1>"M,T,P,L,V"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>